--- a/backend/data/financials_by_company/1183.HK.xlsx
+++ b/backend/data/financials_by_company/1183.HK.xlsx
@@ -4121,7 +4121,7 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>Infinity</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AH2" t="n">
